--- a/Dashboard de Desempenho Odontológico.xlsx
+++ b/Dashboard de Desempenho Odontológico.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fen.impressao04\Desktop\Pag Relatorio dos dentistas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C49218C-8CA4-41F7-AB03-66D17A333D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2F2908-D53A-4353-AB82-809AAF010EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32070" yWindow="2565" windowWidth="14790" windowHeight="11355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard de Desempenho Odontol" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Dentista</t>
   </si>
@@ -131,6 +131,21 @@
   </si>
   <si>
     <t>54 - FERNANDO DA SILVA GOMES</t>
+  </si>
+  <si>
+    <t>901 - CAROLINA DE CARLI FARIAS CRUZ</t>
+  </si>
+  <si>
+    <t>472 - SOFLAUDOS 7 (JESSICA)</t>
+  </si>
+  <si>
+    <t>903 - LUAN DEIVES RODRIGUES LEITE</t>
+  </si>
+  <si>
+    <t>408 - LUANA FERREIRA DA COSTA</t>
+  </si>
+  <si>
+    <t>902 - MONALISA MORAES SILVA NASCIMENTO</t>
   </si>
 </sst>
 </file>
@@ -473,7 +488,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -1876,7 +1891,740 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="10"/>
+      <c r="A59" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="10">
+        <v>60</v>
+      </c>
+      <c r="C59" s="10">
+        <v>20</v>
+      </c>
+      <c r="D59" s="10">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="10">
+        <v>881</v>
+      </c>
+      <c r="F59" s="11">
+        <v>0.73</v>
+      </c>
+      <c r="G59" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="10">
+        <v>50</v>
+      </c>
+      <c r="C60" s="10">
+        <v>20</v>
+      </c>
+      <c r="D60" s="10">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="10">
+        <v>554</v>
+      </c>
+      <c r="F60" s="11">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G60" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="10">
+        <v>70</v>
+      </c>
+      <c r="C61" s="10">
+        <v>20</v>
+      </c>
+      <c r="D61" s="10">
+        <v>1400</v>
+      </c>
+      <c r="E61" s="10">
+        <v>829</v>
+      </c>
+      <c r="F61" s="11">
+        <v>0.59</v>
+      </c>
+      <c r="G61" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="10">
+        <v>60</v>
+      </c>
+      <c r="C62" s="10">
+        <v>20</v>
+      </c>
+      <c r="D62" s="10">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="10">
+        <v>88</v>
+      </c>
+      <c r="F62" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G62" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="10">
+        <v>50</v>
+      </c>
+      <c r="C63" s="10">
+        <v>20</v>
+      </c>
+      <c r="D63" s="10">
+        <v>1000</v>
+      </c>
+      <c r="E63" s="10">
+        <v>454</v>
+      </c>
+      <c r="F63" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="G63" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" s="10">
+        <v>50</v>
+      </c>
+      <c r="C64" s="10">
+        <v>20</v>
+      </c>
+      <c r="D64" s="10">
+        <v>1000</v>
+      </c>
+      <c r="E64" s="10">
+        <v>1114</v>
+      </c>
+      <c r="F64" s="11">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="G64" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="10">
+        <v>100</v>
+      </c>
+      <c r="C65" s="10">
+        <v>20</v>
+      </c>
+      <c r="D65" s="10">
+        <v>2000</v>
+      </c>
+      <c r="E65" s="10">
+        <v>2963</v>
+      </c>
+      <c r="F65" s="11">
+        <v>1.48</v>
+      </c>
+      <c r="G65" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" s="10">
+        <v>100</v>
+      </c>
+      <c r="C66" s="10">
+        <v>20</v>
+      </c>
+      <c r="D66" s="10">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1910</v>
+      </c>
+      <c r="F66" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="G66" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" s="10">
+        <v>60</v>
+      </c>
+      <c r="C67" s="10">
+        <v>20</v>
+      </c>
+      <c r="D67" s="10">
+        <v>1200</v>
+      </c>
+      <c r="E67" s="10">
+        <v>1375</v>
+      </c>
+      <c r="F67" s="11">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G67" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="10">
+        <v>80</v>
+      </c>
+      <c r="C68" s="10">
+        <v>20</v>
+      </c>
+      <c r="D68" s="10">
+        <v>1600</v>
+      </c>
+      <c r="E68" s="10">
+        <v>890</v>
+      </c>
+      <c r="F68" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G68" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" s="10">
+        <v>30</v>
+      </c>
+      <c r="C69" s="10">
+        <v>20</v>
+      </c>
+      <c r="D69" s="10">
+        <v>600</v>
+      </c>
+      <c r="E69" s="10">
+        <v>189</v>
+      </c>
+      <c r="F69" s="11">
+        <v>0.32</v>
+      </c>
+      <c r="G69" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="10">
+        <v>40</v>
+      </c>
+      <c r="C70" s="10">
+        <v>20</v>
+      </c>
+      <c r="D70" s="10">
+        <v>800</v>
+      </c>
+      <c r="E70" s="10">
+        <v>742</v>
+      </c>
+      <c r="F70" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="G70" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B71" s="10">
+        <v>50</v>
+      </c>
+      <c r="C71" s="10">
+        <v>20</v>
+      </c>
+      <c r="D71" s="10">
+        <v>1000</v>
+      </c>
+      <c r="E71" s="10">
+        <v>533</v>
+      </c>
+      <c r="F71" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="G71" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72" s="10">
+        <v>90</v>
+      </c>
+      <c r="C72" s="10">
+        <v>20</v>
+      </c>
+      <c r="D72" s="10">
+        <v>1800</v>
+      </c>
+      <c r="E72" s="10">
+        <v>1613</v>
+      </c>
+      <c r="F72" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G72" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" s="10">
+        <v>30</v>
+      </c>
+      <c r="C73" s="10">
+        <v>20</v>
+      </c>
+      <c r="D73" s="10">
+        <v>600</v>
+      </c>
+      <c r="E73" s="10">
+        <v>259</v>
+      </c>
+      <c r="F73" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="G73" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="10">
+        <v>35</v>
+      </c>
+      <c r="C74" s="10">
+        <v>20</v>
+      </c>
+      <c r="D74" s="10">
+        <v>700</v>
+      </c>
+      <c r="E74" s="10">
+        <v>422</v>
+      </c>
+      <c r="F74" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="G74" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B75" s="10">
+        <v>70</v>
+      </c>
+      <c r="C75" s="10">
+        <v>20</v>
+      </c>
+      <c r="D75" s="10">
+        <v>1400</v>
+      </c>
+      <c r="E75" s="10">
+        <v>1629</v>
+      </c>
+      <c r="F75" s="11">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="G75" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B76" s="10">
+        <v>30</v>
+      </c>
+      <c r="C76" s="10">
+        <v>20</v>
+      </c>
+      <c r="D76" s="10">
+        <v>600</v>
+      </c>
+      <c r="E76" s="10">
+        <v>421</v>
+      </c>
+      <c r="F76" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="G76" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B77" s="10">
+        <v>100</v>
+      </c>
+      <c r="C77" s="10">
+        <v>20</v>
+      </c>
+      <c r="D77" s="10">
+        <v>2000</v>
+      </c>
+      <c r="E77" s="10">
+        <v>1263</v>
+      </c>
+      <c r="F77" s="11">
+        <v>0.63</v>
+      </c>
+      <c r="G77" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78" s="10">
+        <v>30</v>
+      </c>
+      <c r="C78" s="10">
+        <v>20</v>
+      </c>
+      <c r="D78" s="10">
+        <v>600</v>
+      </c>
+      <c r="E78" s="10">
+        <v>206</v>
+      </c>
+      <c r="F78" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="G78" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" s="10">
+        <v>50</v>
+      </c>
+      <c r="C79" s="10">
+        <v>20</v>
+      </c>
+      <c r="D79" s="10">
+        <v>1000</v>
+      </c>
+      <c r="E79" s="10">
+        <v>810</v>
+      </c>
+      <c r="F79" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="G79" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" s="10">
+        <v>40</v>
+      </c>
+      <c r="C80" s="10">
+        <v>20</v>
+      </c>
+      <c r="D80" s="10">
+        <v>800</v>
+      </c>
+      <c r="E80" s="10">
+        <v>606</v>
+      </c>
+      <c r="F80" s="11">
+        <v>0.76</v>
+      </c>
+      <c r="G80" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" s="10">
+        <v>15</v>
+      </c>
+      <c r="C81" s="10">
+        <v>20</v>
+      </c>
+      <c r="D81" s="10">
+        <v>300</v>
+      </c>
+      <c r="E81" s="10">
+        <v>300</v>
+      </c>
+      <c r="F81" s="11">
+        <v>1</v>
+      </c>
+      <c r="G81" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B82" s="10">
+        <v>40</v>
+      </c>
+      <c r="C82" s="10">
+        <v>20</v>
+      </c>
+      <c r="D82" s="10">
+        <v>800</v>
+      </c>
+      <c r="E82" s="10">
+        <v>716</v>
+      </c>
+      <c r="F82" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G82" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B83" s="10">
+        <v>40</v>
+      </c>
+      <c r="C83" s="10">
+        <v>20</v>
+      </c>
+      <c r="D83" s="10">
+        <v>800</v>
+      </c>
+      <c r="E83" s="10">
+        <v>286</v>
+      </c>
+      <c r="F83" s="11">
+        <v>0.36</v>
+      </c>
+      <c r="G83" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" s="10">
+        <v>65</v>
+      </c>
+      <c r="C84" s="10">
+        <v>20</v>
+      </c>
+      <c r="D84" s="10">
+        <v>1300</v>
+      </c>
+      <c r="E84" s="10">
+        <v>1551</v>
+      </c>
+      <c r="F84" s="11">
+        <v>1.19</v>
+      </c>
+      <c r="G84" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B85" s="10">
+        <v>30</v>
+      </c>
+      <c r="C85" s="10">
+        <v>20</v>
+      </c>
+      <c r="D85" s="10">
+        <v>600</v>
+      </c>
+      <c r="E85" s="10">
+        <v>307</v>
+      </c>
+      <c r="F85" s="11">
+        <v>0.51</v>
+      </c>
+      <c r="G85" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" s="10">
+        <v>40</v>
+      </c>
+      <c r="C86" s="10">
+        <v>20</v>
+      </c>
+      <c r="D86" s="10">
+        <v>800</v>
+      </c>
+      <c r="E86" s="10">
+        <v>1268</v>
+      </c>
+      <c r="F86" s="11">
+        <v>1.59</v>
+      </c>
+      <c r="G86" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" s="10">
+        <v>15</v>
+      </c>
+      <c r="C87" s="10">
+        <v>20</v>
+      </c>
+      <c r="D87" s="10">
+        <v>300</v>
+      </c>
+      <c r="E87" s="10">
+        <v>272</v>
+      </c>
+      <c r="F87" s="11">
+        <v>0.91</v>
+      </c>
+      <c r="G87" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B88" s="10">
+        <v>60</v>
+      </c>
+      <c r="C88" s="10">
+        <v>20</v>
+      </c>
+      <c r="D88" s="10">
+        <v>1200</v>
+      </c>
+      <c r="E88" s="10">
+        <v>1009</v>
+      </c>
+      <c r="F88" s="11">
+        <v>0.84</v>
+      </c>
+      <c r="G88" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B89" s="10">
+        <v>40</v>
+      </c>
+      <c r="C89" s="10">
+        <v>20</v>
+      </c>
+      <c r="D89" s="10">
+        <v>800</v>
+      </c>
+      <c r="E89" s="10">
+        <v>2218</v>
+      </c>
+      <c r="F89" s="11">
+        <v>2.77</v>
+      </c>
+      <c r="G89" s="12">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B90" s="10">
+        <v>80</v>
+      </c>
+      <c r="C90" s="10">
+        <v>20</v>
+      </c>
+      <c r="D90" s="10">
+        <v>1600</v>
+      </c>
+      <c r="E90" s="10">
+        <v>893</v>
+      </c>
+      <c r="F90" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G90" s="12">
+        <v>46113</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F30">

--- a/Dashboard de Desempenho Odontológico.xlsx
+++ b/Dashboard de Desempenho Odontológico.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fen.impressao04\Desktop\Pag Relatorio dos dentistas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2F2908-D53A-4353-AB82-809AAF010EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624B5252-A9FD-499E-B1A3-B89769A3D558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32070" yWindow="2565" windowWidth="14790" windowHeight="11355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard de Desempenho Odontol" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="42">
   <si>
     <t>Dentista</t>
   </si>
@@ -488,7 +488,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -2624,6 +2624,742 @@
       </c>
       <c r="G90" s="12">
         <v>46113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" s="10">
+        <v>60</v>
+      </c>
+      <c r="C91" s="10">
+        <v>21</v>
+      </c>
+      <c r="D91" s="10">
+        <v>1260</v>
+      </c>
+      <c r="E91" s="10">
+        <v>935</v>
+      </c>
+      <c r="F91" s="11">
+        <v>0.74</v>
+      </c>
+      <c r="G91" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="10">
+        <v>50</v>
+      </c>
+      <c r="C92" s="10">
+        <v>21</v>
+      </c>
+      <c r="D92" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E92" s="10">
+        <v>361</v>
+      </c>
+      <c r="F92" s="11">
+        <v>0.34</v>
+      </c>
+      <c r="G92" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="10">
+        <v>70</v>
+      </c>
+      <c r="C93" s="10">
+        <v>21</v>
+      </c>
+      <c r="D93" s="10">
+        <v>1470</v>
+      </c>
+      <c r="E93" s="10">
+        <v>815</v>
+      </c>
+      <c r="F93" s="11">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G93" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="10">
+        <v>60</v>
+      </c>
+      <c r="C94" s="10">
+        <v>21</v>
+      </c>
+      <c r="D94" s="10">
+        <v>1260</v>
+      </c>
+      <c r="E94" s="10">
+        <v>559</v>
+      </c>
+      <c r="F94" s="11">
+        <v>0.44</v>
+      </c>
+      <c r="G94" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="10">
+        <v>50</v>
+      </c>
+      <c r="C95" s="10">
+        <v>21</v>
+      </c>
+      <c r="D95" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E95" s="10">
+        <v>554</v>
+      </c>
+      <c r="F95" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="G95" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B96" s="10">
+        <v>50</v>
+      </c>
+      <c r="C96" s="10">
+        <v>21</v>
+      </c>
+      <c r="D96" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E96" s="10">
+        <v>1141</v>
+      </c>
+      <c r="F96" s="11">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="G96" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="10">
+        <v>100</v>
+      </c>
+      <c r="C97" s="10">
+        <v>21</v>
+      </c>
+      <c r="D97" s="10">
+        <v>2100</v>
+      </c>
+      <c r="E97" s="10">
+        <v>3048</v>
+      </c>
+      <c r="F97" s="11">
+        <v>1.45</v>
+      </c>
+      <c r="G97" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B98" s="10">
+        <v>100</v>
+      </c>
+      <c r="C98" s="10">
+        <v>21</v>
+      </c>
+      <c r="D98" s="10">
+        <v>2100</v>
+      </c>
+      <c r="E98" s="10">
+        <v>1883</v>
+      </c>
+      <c r="F98" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G98" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B99" s="10">
+        <v>60</v>
+      </c>
+      <c r="C99" s="10">
+        <v>21</v>
+      </c>
+      <c r="D99" s="10">
+        <v>1260</v>
+      </c>
+      <c r="E99" s="10">
+        <v>1566</v>
+      </c>
+      <c r="F99" s="11">
+        <v>1.24</v>
+      </c>
+      <c r="G99" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" s="10">
+        <v>80</v>
+      </c>
+      <c r="C100" s="10">
+        <v>21</v>
+      </c>
+      <c r="D100" s="10">
+        <v>1680</v>
+      </c>
+      <c r="E100" s="10">
+        <v>665</v>
+      </c>
+      <c r="F100" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="G100" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" s="10">
+        <v>30</v>
+      </c>
+      <c r="C101" s="10">
+        <v>21</v>
+      </c>
+      <c r="D101" s="10">
+        <v>630</v>
+      </c>
+      <c r="E101" s="10">
+        <v>145</v>
+      </c>
+      <c r="F101" s="11">
+        <v>0.23</v>
+      </c>
+      <c r="G101" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B102" s="10">
+        <v>40</v>
+      </c>
+      <c r="C102" s="10">
+        <v>21</v>
+      </c>
+      <c r="D102" s="10">
+        <v>840</v>
+      </c>
+      <c r="E102" s="10">
+        <v>771</v>
+      </c>
+      <c r="F102" s="11">
+        <v>0.92</v>
+      </c>
+      <c r="G102" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B103" s="10">
+        <v>50</v>
+      </c>
+      <c r="C103" s="10">
+        <v>21</v>
+      </c>
+      <c r="D103" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E103" s="10">
+        <v>624</v>
+      </c>
+      <c r="F103" s="11">
+        <v>0.59</v>
+      </c>
+      <c r="G103" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104" s="10">
+        <v>90</v>
+      </c>
+      <c r="C104" s="10">
+        <v>21</v>
+      </c>
+      <c r="D104" s="10">
+        <v>1890</v>
+      </c>
+      <c r="E104" s="10">
+        <v>1774</v>
+      </c>
+      <c r="F104" s="11">
+        <v>0.94</v>
+      </c>
+      <c r="G104" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105" s="10">
+        <v>30</v>
+      </c>
+      <c r="C105" s="10">
+        <v>21</v>
+      </c>
+      <c r="D105" s="10">
+        <v>630</v>
+      </c>
+      <c r="E105" s="10">
+        <v>832</v>
+      </c>
+      <c r="F105" s="11">
+        <v>1.32</v>
+      </c>
+      <c r="G105" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B106" s="10">
+        <v>35</v>
+      </c>
+      <c r="C106" s="10">
+        <v>21</v>
+      </c>
+      <c r="D106" s="10">
+        <v>735</v>
+      </c>
+      <c r="E106" s="10">
+        <v>649</v>
+      </c>
+      <c r="F106" s="11">
+        <v>0.88</v>
+      </c>
+      <c r="G106" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B107" s="10">
+        <v>70</v>
+      </c>
+      <c r="C107" s="10">
+        <v>21</v>
+      </c>
+      <c r="D107" s="10">
+        <v>1470</v>
+      </c>
+      <c r="E107" s="10">
+        <v>1672</v>
+      </c>
+      <c r="F107" s="11">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="G107" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B108" s="10">
+        <v>30</v>
+      </c>
+      <c r="C108" s="10">
+        <v>21</v>
+      </c>
+      <c r="D108" s="10">
+        <v>630</v>
+      </c>
+      <c r="E108" s="10">
+        <v>487</v>
+      </c>
+      <c r="F108" s="11">
+        <v>0.77</v>
+      </c>
+      <c r="G108" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B109" s="10">
+        <v>100</v>
+      </c>
+      <c r="C109" s="10">
+        <v>21</v>
+      </c>
+      <c r="D109" s="10">
+        <v>2100</v>
+      </c>
+      <c r="E109" s="10">
+        <v>1125</v>
+      </c>
+      <c r="F109" s="11">
+        <v>0.54</v>
+      </c>
+      <c r="G109" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B110" s="10">
+        <v>30</v>
+      </c>
+      <c r="C110" s="10">
+        <v>21</v>
+      </c>
+      <c r="D110" s="10">
+        <v>630</v>
+      </c>
+      <c r="E110" s="10">
+        <v>405</v>
+      </c>
+      <c r="F110" s="11">
+        <v>0.64</v>
+      </c>
+      <c r="G110" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111" s="10">
+        <v>50</v>
+      </c>
+      <c r="C111" s="10">
+        <v>21</v>
+      </c>
+      <c r="D111" s="10">
+        <v>1050</v>
+      </c>
+      <c r="E111" s="10">
+        <v>737</v>
+      </c>
+      <c r="F111" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="G111" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B112" s="10">
+        <v>40</v>
+      </c>
+      <c r="C112" s="10">
+        <v>21</v>
+      </c>
+      <c r="D112" s="10">
+        <v>840</v>
+      </c>
+      <c r="E112" s="10">
+        <v>844</v>
+      </c>
+      <c r="F112" s="11">
+        <v>1</v>
+      </c>
+      <c r="G112" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" s="10">
+        <v>15</v>
+      </c>
+      <c r="C113" s="10">
+        <v>21</v>
+      </c>
+      <c r="D113" s="10">
+        <v>315</v>
+      </c>
+      <c r="E113" s="10">
+        <v>303</v>
+      </c>
+      <c r="F113" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="G113" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B114" s="10">
+        <v>40</v>
+      </c>
+      <c r="C114" s="10">
+        <v>21</v>
+      </c>
+      <c r="D114" s="10">
+        <v>840</v>
+      </c>
+      <c r="E114" s="10">
+        <v>664</v>
+      </c>
+      <c r="F114" s="11">
+        <v>0.79</v>
+      </c>
+      <c r="G114" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" s="10">
+        <v>40</v>
+      </c>
+      <c r="C115" s="10">
+        <v>21</v>
+      </c>
+      <c r="D115" s="10">
+        <v>840</v>
+      </c>
+      <c r="E115" s="10">
+        <v>320</v>
+      </c>
+      <c r="F115" s="11">
+        <v>0.38</v>
+      </c>
+      <c r="G115" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B116" s="10">
+        <v>65</v>
+      </c>
+      <c r="C116" s="10">
+        <v>21</v>
+      </c>
+      <c r="D116" s="10">
+        <v>1365</v>
+      </c>
+      <c r="E116" s="10">
+        <v>1471</v>
+      </c>
+      <c r="F116" s="11">
+        <v>1.08</v>
+      </c>
+      <c r="G116" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B117" s="10">
+        <v>30</v>
+      </c>
+      <c r="C117" s="10">
+        <v>21</v>
+      </c>
+      <c r="D117" s="10">
+        <v>630</v>
+      </c>
+      <c r="E117" s="10">
+        <v>401</v>
+      </c>
+      <c r="F117" s="11">
+        <v>0.64</v>
+      </c>
+      <c r="G117" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B118" s="10">
+        <v>40</v>
+      </c>
+      <c r="C118" s="10">
+        <v>21</v>
+      </c>
+      <c r="D118" s="10">
+        <v>840</v>
+      </c>
+      <c r="E118" s="10">
+        <v>885</v>
+      </c>
+      <c r="F118" s="11">
+        <v>1.05</v>
+      </c>
+      <c r="G118" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B119" s="10">
+        <v>15</v>
+      </c>
+      <c r="C119" s="10">
+        <v>21</v>
+      </c>
+      <c r="D119" s="10">
+        <v>315</v>
+      </c>
+      <c r="E119" s="10">
+        <v>162</v>
+      </c>
+      <c r="F119" s="11">
+        <v>0.51</v>
+      </c>
+      <c r="G119" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B120" s="10">
+        <v>60</v>
+      </c>
+      <c r="C120" s="10">
+        <v>21</v>
+      </c>
+      <c r="D120" s="10">
+        <v>1260</v>
+      </c>
+      <c r="E120" s="10">
+        <v>1524</v>
+      </c>
+      <c r="F120" s="11">
+        <v>1.21</v>
+      </c>
+      <c r="G120" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" s="10">
+        <v>40</v>
+      </c>
+      <c r="C121" s="10">
+        <v>21</v>
+      </c>
+      <c r="D121" s="10">
+        <v>840</v>
+      </c>
+      <c r="E121" s="10">
+        <v>1524</v>
+      </c>
+      <c r="F121" s="11">
+        <v>1.81</v>
+      </c>
+      <c r="G121" s="12">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B122" s="10">
+        <v>80</v>
+      </c>
+      <c r="C122" s="10">
+        <v>21</v>
+      </c>
+      <c r="D122" s="10">
+        <v>1680</v>
+      </c>
+      <c r="E122" s="10">
+        <v>1362</v>
+      </c>
+      <c r="F122" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="G122" s="12">
+        <v>46143</v>
       </c>
     </row>
   </sheetData>
